--- a/test-output/excel/HomeLoan_Yearly_Home_Loan_Test.xlsx
+++ b/test-output/excel/HomeLoan_Yearly_Home_Loan_Test.xlsx
@@ -38,31 +38,31 @@
     <t>2026</t>
   </si>
   <si>
-    <t>₹ 11,248</t>
-  </si>
-  <si>
-    <t>₹ 54,342</t>
-  </si>
-  <si>
-    <t>₹ 24,750</t>
-  </si>
-  <si>
-    <t>₹ 90,340</t>
-  </si>
-  <si>
-    <t>₹ 7,98,752</t>
-  </si>
-  <si>
-    <t>1.39%</t>
+    <t>₹ 9,961</t>
+  </si>
+  <si>
+    <t>₹ 48,341</t>
+  </si>
+  <si>
+    <t>₹ 22,000</t>
+  </si>
+  <si>
+    <t>₹ 80,302</t>
+  </si>
+  <si>
+    <t>₹ 8,00,039</t>
+  </si>
+  <si>
+    <t>1.23%</t>
   </si>
   <si>
     <t>2027</t>
   </si>
   <si>
-    <t>₹ 16,224</t>
-  </si>
-  <si>
-    <t>₹ 71,229</t>
+    <t>₹ 16,103</t>
+  </si>
+  <si>
+    <t>₹ 71,350</t>
   </si>
   <si>
     <t>₹ 33,000</t>
@@ -71,292 +71,292 @@
     <t>₹ 1,20,453</t>
   </si>
   <si>
-    <t>₹ 7,82,528</t>
-  </si>
-  <si>
-    <t>3.39%</t>
+    <t>₹ 7,83,936</t>
+  </si>
+  <si>
+    <t>3.22%</t>
   </si>
   <si>
     <t>2028</t>
   </si>
   <si>
-    <t>₹ 17,746</t>
-  </si>
-  <si>
-    <t>₹ 69,707</t>
-  </si>
-  <si>
-    <t>₹ 7,64,782</t>
-  </si>
-  <si>
-    <t>5.58%</t>
+    <t>₹ 17,614</t>
+  </si>
+  <si>
+    <t>₹ 69,839</t>
+  </si>
+  <si>
+    <t>₹ 7,66,322</t>
+  </si>
+  <si>
+    <t>5.39%</t>
   </si>
   <si>
     <t>2029</t>
   </si>
   <si>
-    <t>₹ 19,411</t>
-  </si>
-  <si>
-    <t>₹ 68,043</t>
-  </si>
-  <si>
-    <t>₹ 7,45,371</t>
-  </si>
-  <si>
-    <t>7.98%</t>
+    <t>₹ 19,266</t>
+  </si>
+  <si>
+    <t>₹ 68,187</t>
+  </si>
+  <si>
+    <t>₹ 7,47,056</t>
+  </si>
+  <si>
+    <t>7.77%</t>
   </si>
   <si>
     <t>2030</t>
   </si>
   <si>
-    <t>₹ 21,232</t>
-  </si>
-  <si>
-    <t>₹ 66,222</t>
-  </si>
-  <si>
-    <t>₹ 7,24,139</t>
-  </si>
-  <si>
-    <t>10.6%</t>
+    <t>₹ 21,074</t>
+  </si>
+  <si>
+    <t>₹ 66,380</t>
+  </si>
+  <si>
+    <t>₹ 7,25,982</t>
+  </si>
+  <si>
+    <t>10.37%</t>
   </si>
   <si>
     <t>2031</t>
   </si>
   <si>
-    <t>₹ 23,223</t>
-  </si>
-  <si>
-    <t>₹ 64,230</t>
-  </si>
-  <si>
-    <t>₹ 7,00,916</t>
-  </si>
-  <si>
-    <t>13.47%</t>
+    <t>₹ 23,050</t>
+  </si>
+  <si>
+    <t>₹ 64,403</t>
+  </si>
+  <si>
+    <t>₹ 7,02,932</t>
+  </si>
+  <si>
+    <t>13.22%</t>
   </si>
   <si>
     <t>2032</t>
   </si>
   <si>
-    <t>₹ 25,402</t>
-  </si>
-  <si>
-    <t>₹ 62,052</t>
-  </si>
-  <si>
-    <t>₹ 6,75,514</t>
-  </si>
-  <si>
-    <t>16.6%</t>
+    <t>₹ 25,213</t>
+  </si>
+  <si>
+    <t>₹ 62,241</t>
+  </si>
+  <si>
+    <t>₹ 6,77,719</t>
+  </si>
+  <si>
+    <t>16.33%</t>
   </si>
   <si>
     <t>2033</t>
   </si>
   <si>
-    <t>₹ 27,785</t>
-  </si>
-  <si>
-    <t>₹ 59,669</t>
-  </si>
-  <si>
-    <t>₹ 6,47,729</t>
-  </si>
-  <si>
-    <t>20.03%</t>
+    <t>₹ 27,578</t>
+  </si>
+  <si>
+    <t>₹ 59,876</t>
+  </si>
+  <si>
+    <t>₹ 6,50,141</t>
+  </si>
+  <si>
+    <t>19.74%</t>
   </si>
   <si>
     <t>2034</t>
   </si>
   <si>
-    <t>₹ 30,391</t>
-  </si>
-  <si>
-    <t>₹ 57,062</t>
-  </si>
-  <si>
-    <t>₹ 6,17,338</t>
-  </si>
-  <si>
-    <t>23.79%</t>
+    <t>₹ 30,165</t>
+  </si>
+  <si>
+    <t>₹ 57,289</t>
+  </si>
+  <si>
+    <t>₹ 6,19,976</t>
+  </si>
+  <si>
+    <t>23.46%</t>
   </si>
   <si>
     <t>2035</t>
   </si>
   <si>
-    <t>₹ 33,242</t>
-  </si>
-  <si>
-    <t>₹ 54,211</t>
-  </si>
-  <si>
-    <t>₹ 5,84,096</t>
-  </si>
-  <si>
-    <t>27.89%</t>
+    <t>₹ 32,994</t>
+  </si>
+  <si>
+    <t>₹ 54,459</t>
+  </si>
+  <si>
+    <t>₹ 5,86,982</t>
+  </si>
+  <si>
+    <t>27.53%</t>
   </si>
   <si>
     <t>2036</t>
   </si>
   <si>
-    <t>₹ 36,360</t>
-  </si>
-  <si>
-    <t>₹ 51,093</t>
-  </si>
-  <si>
-    <t>₹ 5,47,736</t>
-  </si>
-  <si>
-    <t>32.38%</t>
+    <t>₹ 36,090</t>
+  </si>
+  <si>
+    <t>₹ 51,364</t>
+  </si>
+  <si>
+    <t>₹ 5,50,892</t>
+  </si>
+  <si>
+    <t>31.99%</t>
   </si>
   <si>
     <t>2037</t>
   </si>
   <si>
-    <t>₹ 39,771</t>
-  </si>
-  <si>
-    <t>₹ 47,682</t>
-  </si>
-  <si>
-    <t>₹ 5,07,965</t>
-  </si>
-  <si>
-    <t>37.29%</t>
+    <t>₹ 39,475</t>
+  </si>
+  <si>
+    <t>₹ 47,978</t>
+  </si>
+  <si>
+    <t>₹ 5,11,417</t>
+  </si>
+  <si>
+    <t>36.86%</t>
   </si>
   <si>
     <t>2038</t>
   </si>
   <si>
-    <t>₹ 43,502</t>
-  </si>
-  <si>
-    <t>₹ 43,951</t>
-  </si>
-  <si>
-    <t>₹ 4,64,463</t>
-  </si>
-  <si>
-    <t>42.66%</t>
+    <t>₹ 43,178</t>
+  </si>
+  <si>
+    <t>₹ 44,275</t>
+  </si>
+  <si>
+    <t>₹ 4,68,239</t>
+  </si>
+  <si>
+    <t>42.19%</t>
   </si>
   <si>
     <t>2039</t>
   </si>
   <si>
-    <t>₹ 47,583</t>
-  </si>
-  <si>
-    <t>₹ 39,871</t>
-  </si>
-  <si>
-    <t>₹ 4,16,880</t>
-  </si>
-  <si>
-    <t>48.53%</t>
+    <t>₹ 47,228</t>
+  </si>
+  <si>
+    <t>₹ 40,225</t>
+  </si>
+  <si>
+    <t>₹ 4,21,011</t>
+  </si>
+  <si>
+    <t>48.02%</t>
   </si>
   <si>
     <t>2040</t>
   </si>
   <si>
-    <t>₹ 52,046</t>
-  </si>
-  <si>
-    <t>₹ 35,407</t>
-  </si>
-  <si>
-    <t>₹ 3,64,834</t>
-  </si>
-  <si>
-    <t>54.96%</t>
+    <t>₹ 51,659</t>
+  </si>
+  <si>
+    <t>₹ 35,795</t>
+  </si>
+  <si>
+    <t>₹ 3,69,352</t>
+  </si>
+  <si>
+    <t>54.4%</t>
   </si>
   <si>
     <t>2041</t>
   </si>
   <si>
-    <t>₹ 56,929</t>
-  </si>
-  <si>
-    <t>₹ 30,525</t>
-  </si>
-  <si>
-    <t>₹ 3,07,906</t>
-  </si>
-  <si>
-    <t>61.99%</t>
+    <t>₹ 56,505</t>
+  </si>
+  <si>
+    <t>₹ 30,949</t>
+  </si>
+  <si>
+    <t>₹ 3,12,847</t>
+  </si>
+  <si>
+    <t>61.38%</t>
   </si>
   <si>
     <t>2042</t>
   </si>
   <si>
-    <t>₹ 62,269</t>
-  </si>
-  <si>
-    <t>₹ 25,184</t>
-  </si>
-  <si>
-    <t>₹ 2,45,637</t>
-  </si>
-  <si>
-    <t>69.67%</t>
+    <t>₹ 61,805</t>
+  </si>
+  <si>
+    <t>₹ 25,648</t>
+  </si>
+  <si>
+    <t>₹ 2,51,042</t>
+  </si>
+  <si>
+    <t>69.01%</t>
   </si>
   <si>
     <t>2043</t>
   </si>
   <si>
-    <t>₹ 68,110</t>
-  </si>
-  <si>
-    <t>₹ 19,343</t>
-  </si>
-  <si>
-    <t>₹ 1,77,527</t>
-  </si>
-  <si>
-    <t>78.08%</t>
+    <t>₹ 67,603</t>
+  </si>
+  <si>
+    <t>₹ 19,850</t>
+  </si>
+  <si>
+    <t>₹ 1,83,439</t>
+  </si>
+  <si>
+    <t>77.35%</t>
   </si>
   <si>
     <t>2044</t>
   </si>
   <si>
-    <t>₹ 74,499</t>
-  </si>
-  <si>
-    <t>₹ 12,954</t>
-  </si>
-  <si>
-    <t>₹ 1,03,027</t>
-  </si>
-  <si>
-    <t>87.28%</t>
+    <t>₹ 73,945</t>
+  </si>
+  <si>
+    <t>₹ 13,509</t>
+  </si>
+  <si>
+    <t>₹ 1,09,494</t>
+  </si>
+  <si>
+    <t>86.48%</t>
   </si>
   <si>
     <t>2045</t>
   </si>
   <si>
-    <t>₹ 81,488</t>
-  </si>
-  <si>
-    <t>₹ 5,965</t>
-  </si>
-  <si>
-    <t>₹ 21,539</t>
-  </si>
-  <si>
-    <t>97.34%</t>
+    <t>₹ 80,881</t>
+  </si>
+  <si>
+    <t>₹ 6,572</t>
+  </si>
+  <si>
+    <t>₹ 28,613</t>
+  </si>
+  <si>
+    <t>96.47%</t>
   </si>
   <si>
     <t>2046</t>
   </si>
   <si>
-    <t>₹ 324</t>
-  </si>
-  <si>
-    <t>₹ 8,250</t>
-  </si>
-  <si>
-    <t>₹ 30,113</t>
+    <t>₹ 538</t>
+  </si>
+  <si>
+    <t>₹ 11,000</t>
+  </si>
+  <si>
+    <t>₹ 40,151</t>
   </si>
   <si>
     <t>₹ 0</t>
